--- a/data/dividends_info_20260710.xlsx
+++ b/data/dividends_info_20260710.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>62.63999938964844</v>
+        <v>62</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1436781623195113</v>
+        <v>0.1451612903225806</v>
       </c>
       <c r="J2" t="n">
         <v>248</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>65.19999694824219</v>
+        <v>65.15000152587891</v>
       </c>
       <c r="I3" t="n">
-        <v>1.073619682153792</v>
+        <v>1.07444356654688</v>
       </c>
       <c r="J3" t="n">
         <v>227</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>9.800000190734863</v>
+        <v>9.739999771118164</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6122448860432199</v>
+        <v>0.6160164415805928</v>
       </c>
       <c r="J4" t="n">
         <v>157</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>62.63999938964844</v>
+        <v>62</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1436781623195113</v>
+        <v>0.1451612903225806</v>
       </c>
       <c r="J6" t="n">
         <v>157</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2.099999904632568</v>
+        <v>2.109999895095825</v>
       </c>
       <c r="I7" t="n">
-        <v>3.666666833181238</v>
+        <v>3.649289280960038</v>
       </c>
       <c r="J7" t="n">
         <v>136</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>20.93499946594238</v>
+        <v>20.7549991607666</v>
       </c>
       <c r="I8" t="n">
-        <v>1.289706266480891</v>
+        <v>1.300891404083427</v>
       </c>
       <c r="J8" t="n">
         <v>136</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>6.079999923706055</v>
+        <v>5.949999809265137</v>
       </c>
       <c r="I9" t="n">
-        <v>3.289473725487982</v>
+        <v>3.36134464556733</v>
       </c>
       <c r="J9" t="n">
         <v>129</v>
@@ -899,10 +899,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>7.400000095367432</v>
+        <v>6.800000190734863</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8108108003614941</v>
+        <v>0.8823529164271378</v>
       </c>
       <c r="J10" t="n">
         <v>101</v>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>4.920000076293945</v>
+        <v>4.900000095367432</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7723577116003624</v>
+        <v>0.7755101889880786</v>
       </c>
       <c r="J13" t="n">
         <v>80</v>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>20.93499946594238</v>
+        <v>20.7549991607666</v>
       </c>
       <c r="I14" t="n">
-        <v>1.289706266480891</v>
+        <v>1.300891404083427</v>
       </c>
       <c r="J14" t="n">
         <v>73</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>62.63999938964844</v>
+        <v>62</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1436781623195113</v>
+        <v>0.1451612903225806</v>
       </c>
       <c r="J15" t="n">
         <v>73</v>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>6</v>
+        <v>5.940000057220459</v>
       </c>
       <c r="I16" t="n">
-        <v>5</v>
+        <v>5.050505001853162</v>
       </c>
       <c r="J16" t="n">
         <v>66</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>4.920000076293945</v>
+        <v>4.900000095367432</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7723577116003624</v>
+        <v>0.7755101889880786</v>
       </c>
       <c r="J18" t="n">
         <v>24</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>5.789999961853027</v>
+        <v>5.800000190734863</v>
       </c>
       <c r="I19" t="n">
-        <v>4.317789320329981</v>
+        <v>4.310344685839137</v>
       </c>
       <c r="J19" t="n">
         <v>17</v>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>10.13599967956543</v>
+        <v>10.11999988555908</v>
       </c>
       <c r="I21" t="n">
-        <v>2.565114524659764</v>
+        <v>2.569169989527488</v>
       </c>
       <c r="J21" t="n">
         <v>10</v>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>14.72000026702881</v>
+        <v>14.77999973297119</v>
       </c>
       <c r="I22" t="n">
-        <v>4.076086882579305</v>
+        <v>4.059539992152512</v>
       </c>
       <c r="J22" t="n">
         <v>10</v>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>2.799999952316284</v>
+        <v>2.79200005531311</v>
       </c>
       <c r="I23" t="n">
-        <v>7.857142990949205</v>
+        <v>7.879656004352334</v>
       </c>
       <c r="J23" t="n">
         <v>10</v>
@@ -1604,10 +1604,10 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>6.744999885559082</v>
+        <v>6.880000114440918</v>
       </c>
       <c r="I25" t="n">
-        <v>3.558191313150879</v>
+        <v>3.488372034998183</v>
       </c>
       <c r="J25" t="n">
         <v>10</v>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>19.85000038146973</v>
+        <v>18.89999961853027</v>
       </c>
       <c r="I26" t="n">
-        <v>1.89420651271625</v>
+        <v>1.989418029571574</v>
       </c>
       <c r="J26" t="n">
         <v>10</v>
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>4</v>
+        <v>3.960000038146973</v>
       </c>
       <c r="I27" t="n">
-        <v>1.48635</v>
+        <v>1.50136362190089</v>
       </c>
       <c r="J27" t="n">
         <v>3</v>
@@ -1839,10 +1839,10 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>3.299999952316284</v>
+        <v>3.220000028610229</v>
       </c>
       <c r="I30" t="n">
-        <v>4.545454611134596</v>
+        <v>4.658385051777184</v>
       </c>
       <c r="J30" t="n">
         <v>3</v>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>2.140000104904175</v>
+        <v>2.200000047683716</v>
       </c>
       <c r="I31" t="n">
-        <v>3.971962422114281</v>
+        <v>3.863636279894303</v>
       </c>
       <c r="J31" t="n">
         <v>-4</v>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>36</v>
+        <v>36.40000152587891</v>
       </c>
       <c r="I33" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.4120878948132904</v>
       </c>
       <c r="J33" t="n">
         <v>-4</v>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>9.600000381469727</v>
+        <v>9.550000190734863</v>
       </c>
       <c r="I34" t="n">
-        <v>23.25937407575551</v>
+        <v>23.38115136548684</v>
       </c>
       <c r="J34" t="n">
         <v>-4</v>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>5.199999809265137</v>
+        <v>5.25</v>
       </c>
       <c r="I35" t="n">
-        <v>0.7692307974459868</v>
+        <v>0.7619047619047619</v>
       </c>
       <c r="J35" t="n">
         <v>-11</v>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>21.3799991607666</v>
+        <v>21.31999969482422</v>
       </c>
       <c r="I36" t="n">
-        <v>1.169317164702059</v>
+        <v>1.172607896709734</v>
       </c>
       <c r="J36" t="n">
         <v>-18</v>
@@ -2168,10 +2168,10 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>28.20000076293945</v>
+        <v>28.54999923706055</v>
       </c>
       <c r="I37" t="n">
-        <v>0.6914893429941666</v>
+        <v>0.6830122774464803</v>
       </c>
       <c r="J37" t="n">
         <v>-18</v>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>1.870000004768372</v>
+        <v>1.884999990463257</v>
       </c>
       <c r="I38" t="n">
-        <v>1.764705877853063</v>
+        <v>1.75066313883057</v>
       </c>
       <c r="J38" t="n">
         <v>-18</v>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>5.110000133514404</v>
+        <v>5.15500020980835</v>
       </c>
       <c r="I39" t="n">
-        <v>5.67514662275659</v>
+        <v>5.62560597860347</v>
       </c>
       <c r="J39" t="n">
         <v>-18</v>
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>3.789999961853027</v>
+        <v>3.793999910354614</v>
       </c>
       <c r="I40" t="n">
-        <v>4.221635926396472</v>
+        <v>4.217185128637635</v>
       </c>
       <c r="J40" t="n">
         <v>-18</v>
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>2.53600001335144</v>
+        <v>2.532000064849854</v>
       </c>
       <c r="I41" t="n">
-        <v>5.465299655769076</v>
+        <v>5.473933509090132</v>
       </c>
       <c r="J41" t="n">
         <v>-18</v>
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>51.58000183105469</v>
+        <v>51.81999969482422</v>
       </c>
       <c r="I42" t="n">
-        <v>1.221403601464583</v>
+        <v>1.215746823060913</v>
       </c>
       <c r="J42" t="n">
         <v>-18</v>
@@ -2450,10 +2450,10 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>6.175000190734863</v>
+        <v>6.195000171661377</v>
       </c>
       <c r="I43" t="n">
-        <v>2.267206407702785</v>
+        <v>2.259886943029007</v>
       </c>
       <c r="J43" t="n">
         <v>-18</v>
@@ -2497,10 +2497,10 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>16.85000038146973</v>
+        <v>16.39999961853027</v>
       </c>
       <c r="I44" t="n">
-        <v>4.629080013895912</v>
+        <v>4.756097671604103</v>
       </c>
       <c r="J44" t="n">
         <v>-18</v>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>28.72999954223633</v>
+        <v>28.70000076293945</v>
       </c>
       <c r="I45" t="n">
-        <v>2.958579928796742</v>
+        <v>2.961672395136699</v>
       </c>
       <c r="J45" t="n">
         <v>-18</v>
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>62.63999938964844</v>
+        <v>62</v>
       </c>
       <c r="I46" t="n">
-        <v>0.1436781623195113</v>
+        <v>0.1451612903225806</v>
       </c>
       <c r="J46" t="n">
         <v>-18</v>
@@ -2638,10 +2638,10 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>1.409999966621399</v>
+        <v>1.519999980926514</v>
       </c>
       <c r="I47" t="n">
-        <v>0.709219874945225</v>
+        <v>0.6578947450975963</v>
       </c>
       <c r="J47" t="n">
         <v>-18</v>
@@ -2685,10 +2685,10 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>6.179999828338623</v>
+        <v>6.170000076293945</v>
       </c>
       <c r="I48" t="n">
-        <v>2.933657039416765</v>
+        <v>2.938411633033546</v>
       </c>
       <c r="J48" t="n">
         <v>-18</v>
@@ -2732,10 +2732,10 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>9.670000076293945</v>
+        <v>9.729999542236328</v>
       </c>
       <c r="I49" t="n">
-        <v>2.688728003605619</v>
+        <v>2.672148121604557</v>
       </c>
       <c r="J49" t="n">
         <v>-18</v>
@@ -2779,10 +2779,10 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>10.17500019073486</v>
+        <v>10.24499988555908</v>
       </c>
       <c r="I50" t="n">
-        <v>2.722358671326909</v>
+        <v>2.703757960900004</v>
       </c>
       <c r="J50" t="n">
         <v>-18</v>
@@ -2826,10 +2826,10 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>1.144999980926514</v>
+        <v>1.134999990463257</v>
       </c>
       <c r="I51" t="n">
-        <v>1.179039320950559</v>
+        <v>1.189427322769395</v>
       </c>
       <c r="J51" t="n">
         <v>-25</v>
@@ -2873,10 +2873,10 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>2.936000108718872</v>
+        <v>2.940000057220459</v>
       </c>
       <c r="I52" t="n">
-        <v>3.746593866714762</v>
+        <v>3.741496525819677</v>
       </c>
       <c r="J52" t="n">
         <v>-25</v>
@@ -2920,10 +2920,10 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>1.649999976158142</v>
+        <v>1.639999985694885</v>
       </c>
       <c r="I53" t="n">
-        <v>1.454545475563071</v>
+        <v>1.463414646911167</v>
       </c>
       <c r="J53" t="n">
         <v>-25</v>
@@ -4224,7 +4224,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Ariston Holding N.V.</t>
+          <t>Banca Generali S.p.A.</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -4234,7 +4234,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -4275,7 +4275,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Acinque S.p.A.</t>
+          <t>Ariston Holding N.V.</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -4292,7 +4292,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>BREMBO N.V.</t>
+          <t>Ariston Holding N.V.</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -4302,14 +4302,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Banca Generali S.p.A.</t>
+          <t>BREMBO N.V.</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -4377,7 +4377,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Ariston Holding N.V.</t>
+          <t>Acinque S.p.A.</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -4479,7 +4479,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Datrix S.p.A.</t>
+          <t>FINCANTIERI S.p.A.</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -4489,14 +4489,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>FINCANTIERI S.p.A.</t>
+          <t>Datrix S.p.A.</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -4506,14 +4506,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>IREN S.p.A.</t>
+          <t>Leonardo S.p.A.</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -4530,7 +4530,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Gabetti Property Solutions S.p.A.</t>
+          <t>Kruso Kapital S.p.A.</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -4547,7 +4547,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>KALEON S.P.A.</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4564,7 +4564,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>Iveco Group N.V.</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4574,14 +4574,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>REPLY S.p.A.</t>
+          <t>Intred S.p.A.</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4591,14 +4591,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Prysmian S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4615,7 +4615,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>RAI WAY S.p.A.</t>
+          <t>Gabetti Property Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -4632,7 +4632,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Pozzi Milano S.p.A.</t>
+          <t>IREN S.p.A.</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -4642,14 +4642,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Misitano &amp; Stracuzzi S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -4659,14 +4659,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>ZIGNAGO VETRO S.p.A.</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -4683,7 +4683,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4693,14 +4693,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>RCS MediaGroup S.p.A.</t>
+          <t>Lottomatica Group S.p.A.</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4710,14 +4710,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>Toscana Aeroporti S.p.A.</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4727,14 +4727,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -4744,14 +4744,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Iveco Group N.V.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -4768,7 +4768,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>KALEON S.P.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -4785,7 +4785,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Kruso Kapital S.p.A.</t>
+          <t>Misitano &amp; Stracuzzi S.p.A.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -4795,14 +4795,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Leonardo S.p.A.</t>
+          <t>Tinexta S.p.A.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -4819,7 +4819,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -4836,7 +4836,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>ESAUTOMOTION S.p.A.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -4846,14 +4846,14 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -4870,7 +4870,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -4887,7 +4887,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Tinexta S.p.A.</t>
+          <t>ELICA S.p.A.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -4904,7 +4904,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Toscana Aeroporti S.p.A.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -4914,14 +4914,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -4931,14 +4931,14 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -4948,14 +4948,14 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>REPLY S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -4972,7 +4972,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Intred S.p.A.</t>
+          <t>RCS MediaGroup S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -4982,14 +4982,14 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Lottomatica Group S.p.A.</t>
+          <t>RAI WAY S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -4999,14 +4999,14 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
+          <t>Prysmian S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -5016,14 +5016,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>Pozzi Milano S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -5033,14 +5033,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Alerion Clean Power S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -5057,7 +5057,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>BANCA MEDIOLANUM S.p.A.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -5067,14 +5067,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -5084,14 +5084,14 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -5101,14 +5101,14 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -5118,14 +5118,14 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
@@ -5159,7 +5159,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -5169,14 +5169,14 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -5186,14 +5186,14 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -5203,14 +5203,14 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -5227,7 +5227,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>BANCA MEDIOLANUM S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -5237,14 +5237,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -5254,14 +5254,14 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>AEDES S.p.A.</t>
+          <t>Alerion Clean Power S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -5278,7 +5278,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -5295,7 +5295,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -5312,7 +5312,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>ESAUTOMOTION S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -5322,14 +5322,14 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -5346,7 +5346,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -5356,14 +5356,14 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>ELICA S.p.A.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -5373,14 +5373,14 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>AEDES S.p.A.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -5397,7 +5397,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>A2A S.p.A.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -5407,14 +5407,14 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>AZIMUT HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -5424,14 +5424,14 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>AZIMUT HOLDING S.p.A.</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -5441,14 +5441,14 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -5458,14 +5458,14 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -5475,14 +5475,14 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -5499,7 +5499,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>BIESSE S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -5516,7 +5516,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>CAIRO COMMUNICATION S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -5543,14 +5543,14 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -5567,7 +5567,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>CIR S.p.A. - COMPAGNIE INDUSTRIALI RIUNITE</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -5584,7 +5584,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>BIESSE S.p.A.</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -5594,7 +5594,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -5618,7 +5618,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>DiaSorin S.p.A</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -5628,14 +5628,14 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>CIR S.p.A. - COMPAGNIE INDUSTRIALI RIUNITE</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -5652,7 +5652,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Ferretti S.p.A.</t>
+          <t>CAIRO COMMUNICATION S.p.A.</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -5669,7 +5669,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>DiaSorin S.p.A</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -5679,14 +5679,14 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Misitano &amp; Stracuzzi S.p.A.</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -5696,14 +5696,14 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Nusco S.p.A.</t>
+          <t>GREEN OLEO S.p.A</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -5720,7 +5720,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Svas Biosana S.p.A.</t>
+          <t>Tinexta S.p.A.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -5730,14 +5730,14 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Tinexta S.p.A.</t>
+          <t>Misitano &amp; Stracuzzi S.p.A.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -5747,14 +5747,14 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>Svas Biosana S.p.A.</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -5764,14 +5764,14 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>Nusco S.p.A.</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -5788,7 +5788,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
+          <t>CLABO S.p.A.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -5798,14 +5798,14 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>ENAV S.p.A.</t>
+          <t>Anima Holding S.p.A.</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -5822,7 +5822,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Anima Holding S.p.A.</t>
+          <t>Alfonsino S.p.A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -5839,7 +5839,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Alfonsino S.p.A.</t>
+          <t>EuroGroup Laminations S.p.A.</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -5873,7 +5873,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>CLABO S.p.A.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -5883,14 +5883,14 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>EuroGroup Laminations S.p.A.</t>
+          <t>ENAV S.p.A.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -5907,7 +5907,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>IGD SIIQ S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -5924,7 +5924,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>DATALOGIC S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -5934,14 +5934,14 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>CREDITO EMILIANO S.p.A.</t>
+          <t>BUZZI S.p.A.</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -5975,7 +5975,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>BUZZI S.p.A.</t>
+          <t>CREDITO EMILIANO S.p.A.</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -5992,7 +5992,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>DATALOGIC S.p.A.</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -6002,14 +6002,14 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>IGD SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -6026,7 +6026,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>SAFILO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -6043,7 +6043,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -6053,14 +6053,14 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -6077,7 +6077,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>SAFILO GROUP S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -6087,14 +6087,14 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -6121,14 +6121,14 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -6138,14 +6138,14 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Banco BPM S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -6162,7 +6162,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -6172,14 +6172,14 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -6189,14 +6189,14 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>PIQUADRO S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -6206,14 +6206,14 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Bper Banca S.P.A.</t>
+          <t>Technoprobe S.p.A.</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -6230,7 +6230,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>doValue S.p.A.</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -6247,7 +6247,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>INTERPUMP GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -6257,14 +6257,14 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>Masi Agricola S.p.A.</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -6281,7 +6281,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Masi Agricola S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -6308,14 +6308,14 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Technoprobe S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -6325,14 +6325,14 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -6342,14 +6342,14 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>PIQUADRO S.p.A.</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -6359,14 +6359,14 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>Bper Banca S.P.A.</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -6376,14 +6376,14 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>doValue S.p.A.</t>
+          <t>Banco BPM S.p.A.</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -6400,7 +6400,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>INTERPUMP GROUP S.p.A.</t>
+          <t>BFF Bank S.P.A.</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -6417,7 +6417,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>BFF Bank S.P.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -6434,7 +6434,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -6444,14 +6444,14 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -6461,14 +6461,14 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>REVO Insurance S.p.A.</t>
+          <t>PROMOTICA S.p.A.</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -6478,14 +6478,14 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>TXT E-SOLUTIONS S.p.A.</t>
+          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -6502,7 +6502,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Unipol S.p.A.</t>
+          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -6519,7 +6519,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>GVS S.p.A.</t>
+          <t>BANCA SISTEMA S.p.A.</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -6529,14 +6529,14 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
+          <t>GEFRAN S.p.A.</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -6553,7 +6553,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Bper Banca S.P.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -6563,14 +6563,14 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>F.I.L.A. S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -6580,14 +6580,14 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>GEFRAN S.p.A.</t>
+          <t>Abitare In S.p.A.</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -6597,14 +6597,14 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
+          <t>BANCA SISTEMA S.p.A.</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -6621,7 +6621,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
+          <t>GVS S.p.A.</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -6638,7 +6638,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>Bper Banca S.P.A.</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -6655,7 +6655,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>PROMOTICA S.p.A.</t>
+          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -6665,14 +6665,14 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -6682,14 +6682,14 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>F.I.L.A. S.p.A.</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -6699,14 +6699,14 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Abitare In S.p.A.</t>
+          <t>REVO Insurance S.p.A.</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -6716,14 +6716,14 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>BANCA SISTEMA S.p.A.</t>
+          <t>TXT E-SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -6740,7 +6740,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>BANCA SISTEMA S.p.A.</t>
+          <t>Unipol S.p.A.</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -6750,14 +6750,14 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
+          <t>EMAK S.p.A.</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -6774,7 +6774,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>EMAK S.p.A.</t>
+          <t>Riba Mundo Tecnologia S.A.</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -6784,14 +6784,14 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Riba Mundo Tecnologia S.A.</t>
+          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -6801,7 +6801,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -6829,78 +6829,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>CASTELLO SGR S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Sesa S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Tinexta S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>